--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/183.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/183.xlsx
@@ -426,13 +426,13 @@
         <v>4.055430662511267</v>
       </c>
       <c r="E2">
-        <v>-15.40645482394915</v>
+        <v>-11.67210760368589</v>
       </c>
       <c r="F2">
-        <v>-4.039675437825176</v>
+        <v>-3.996436316133847</v>
       </c>
       <c r="G2">
-        <v>-10.48012564288281</v>
+        <v>-7.539487219987624</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>3.599360727155333</v>
       </c>
       <c r="E3">
-        <v>-16.86567406038878</v>
+        <v>-11.49023955906384</v>
       </c>
       <c r="F3">
-        <v>-4.188688793179973</v>
+        <v>-3.986697200579133</v>
       </c>
       <c r="G3">
-        <v>-9.110152377276064</v>
+        <v>-7.673316023412662</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>3.095746152399653</v>
       </c>
       <c r="E4">
-        <v>-15.74160718525683</v>
+        <v>-12.21561052561248</v>
       </c>
       <c r="F4">
-        <v>-4.186198720767158</v>
+        <v>-3.955475204800217</v>
       </c>
       <c r="G4">
-        <v>-9.428620237062875</v>
+        <v>-7.216149547712547</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>2.603673479012313</v>
       </c>
       <c r="E5">
-        <v>-15.51471705205052</v>
+        <v>-12.56308486469503</v>
       </c>
       <c r="F5">
-        <v>-3.944978961439344</v>
+        <v>-3.597265945542433</v>
       </c>
       <c r="G5">
-        <v>-9.51898819864836</v>
+        <v>-6.791433039388368</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>2.142434334620227</v>
       </c>
       <c r="E6">
-        <v>-16.86988101274191</v>
+        <v>-13.44724677232263</v>
       </c>
       <c r="F6">
-        <v>-4.326931715563571</v>
+        <v>-4.006119931072573</v>
       </c>
       <c r="G6">
-        <v>-9.646341574998583</v>
+        <v>-7.176903030344487</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>1.746317379844945</v>
       </c>
       <c r="E7">
-        <v>-16.19278357911504</v>
+        <v>-13.88888619992068</v>
       </c>
       <c r="F7">
-        <v>-4.005963369633444</v>
+        <v>-3.70833344690979</v>
       </c>
       <c r="G7">
-        <v>-9.843266065856589</v>
+        <v>-7.114893201848398</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>1.433053894024881</v>
       </c>
       <c r="E8">
-        <v>-17.1042023717948</v>
+        <v>-15.02653849707564</v>
       </c>
       <c r="F8">
-        <v>-4.298472325072992</v>
+        <v>-3.705363749770754</v>
       </c>
       <c r="G8">
-        <v>-8.978640955728515</v>
+        <v>-5.989347445042666</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>1.223229570269195</v>
       </c>
       <c r="E9">
-        <v>-19.15878461449687</v>
+        <v>-14.73233712621932</v>
       </c>
       <c r="F9">
-        <v>-3.552500142727745</v>
+        <v>-3.842468495342906</v>
       </c>
       <c r="G9">
-        <v>-8.021582103598451</v>
+        <v>-5.985715776586085</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>1.129879791151918</v>
       </c>
       <c r="E10">
-        <v>-19.87501259202402</v>
+        <v>-15.05821064428529</v>
       </c>
       <c r="F10">
-        <v>-4.036974131724646</v>
+        <v>-3.721230299003976</v>
       </c>
       <c r="G10">
-        <v>-8.163733618509218</v>
+        <v>-6.389397078553736</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>1.156523733166793</v>
       </c>
       <c r="E11">
-        <v>-19.15758004041083</v>
+        <v>-15.81596925693679</v>
       </c>
       <c r="F11">
-        <v>-3.824541796378921</v>
+        <v>-3.418900219636837</v>
       </c>
       <c r="G11">
-        <v>-7.538811868697613</v>
+        <v>-6.471922357756688</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.292699919112219</v>
       </c>
       <c r="E12">
-        <v>-19.64376606682233</v>
+        <v>-16.36860611093685</v>
       </c>
       <c r="F12">
-        <v>-4.189840223869864</v>
+        <v>-3.460880222875911</v>
       </c>
       <c r="G12">
-        <v>-8.436115373843833</v>
+        <v>-5.304067828959069</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.522019955577994</v>
       </c>
       <c r="E13">
-        <v>-20.81736539065018</v>
+        <v>-17.94606833219076</v>
       </c>
       <c r="F13">
-        <v>-3.764024587400001</v>
+        <v>-3.701615387273086</v>
       </c>
       <c r="G13">
-        <v>-7.931346563834537</v>
+        <v>-5.458908664921862</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.824522509498236</v>
       </c>
       <c r="E14">
-        <v>-21.1414954462232</v>
+        <v>-17.54725015480924</v>
       </c>
       <c r="F14">
-        <v>-3.408710472215001</v>
+        <v>-3.373707807609708</v>
       </c>
       <c r="G14">
-        <v>-8.218370862089349</v>
+        <v>-4.347829992122744</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.171212496616254</v>
       </c>
       <c r="E15">
-        <v>-21.36079132851864</v>
+        <v>-18.04472566692187</v>
       </c>
       <c r="F15">
-        <v>-2.921482989971193</v>
+        <v>-3.072055332778059</v>
       </c>
       <c r="G15">
-        <v>-8.04688791370064</v>
+        <v>-4.679553276248796</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.533121302952499</v>
       </c>
       <c r="E16">
-        <v>-22.44681449351215</v>
+        <v>-18.94338774832203</v>
       </c>
       <c r="F16">
-        <v>-3.351872871239315</v>
+        <v>-3.136892477762579</v>
       </c>
       <c r="G16">
-        <v>-7.144165045506634</v>
+        <v>-4.546456103387936</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>2.885684282890745</v>
       </c>
       <c r="E17">
-        <v>-21.81853853816197</v>
+        <v>-19.87421558059867</v>
       </c>
       <c r="F17">
-        <v>-2.545920261992161</v>
+        <v>-2.302802712944535</v>
       </c>
       <c r="G17">
-        <v>-5.738775563720769</v>
+        <v>-4.305680126316743</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.207449423737069</v>
       </c>
       <c r="E18">
-        <v>-24.50494705983623</v>
+        <v>-20.32560028426123</v>
       </c>
       <c r="F18">
-        <v>-3.027263022206482</v>
+        <v>-2.614893445418859</v>
       </c>
       <c r="G18">
-        <v>-5.909738756459812</v>
+        <v>-4.07893755178652</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.477458498385468</v>
       </c>
       <c r="E19">
-        <v>-24.03211550327335</v>
+        <v>-20.38712413212944</v>
       </c>
       <c r="F19">
-        <v>-1.98476761598772</v>
+        <v>-2.4332241903109</v>
       </c>
       <c r="G19">
-        <v>-6.212570909664644</v>
+        <v>-4.234142547758633</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.680951638001639</v>
       </c>
       <c r="E20">
-        <v>-25.56544774532251</v>
+        <v>-22.06665815751624</v>
       </c>
       <c r="F20">
-        <v>-2.170741068120626</v>
+        <v>-1.866376518412212</v>
       </c>
       <c r="G20">
-        <v>-6.765100960169005</v>
+        <v>-4.25468448282981</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.808086615980313</v>
       </c>
       <c r="E21">
-        <v>-27.06487983095026</v>
+        <v>-21.71873097103292</v>
       </c>
       <c r="F21">
-        <v>-1.94773296614336</v>
+        <v>-1.816089646857866</v>
       </c>
       <c r="G21">
-        <v>-7.1454098106294</v>
+        <v>-3.355119875080268</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.853335080695399</v>
       </c>
       <c r="E22">
-        <v>-24.9504945605029</v>
+        <v>-22.50817531631609</v>
       </c>
       <c r="F22">
-        <v>-2.003473808677739</v>
+        <v>-1.787660077593787</v>
       </c>
       <c r="G22">
-        <v>-6.762383002281263</v>
+        <v>-3.57205330317763</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.81478052929479</v>
       </c>
       <c r="E23">
-        <v>-24.61304626287333</v>
+        <v>-22.75125021562581</v>
       </c>
       <c r="F23">
-        <v>-1.77679272563646</v>
+        <v>-1.763442756572943</v>
       </c>
       <c r="G23">
-        <v>-6.276567065484294</v>
+        <v>-3.213961523831284</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.696271149119586</v>
       </c>
       <c r="E24">
-        <v>-27.16643538904627</v>
+        <v>-23.10933929778234</v>
       </c>
       <c r="F24">
-        <v>-1.548649574129239</v>
+        <v>-1.395037951321502</v>
       </c>
       <c r="G24">
-        <v>-6.494040112504559</v>
+        <v>-3.711112768554717</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.506803412429785</v>
       </c>
       <c r="E25">
-        <v>-26.89139852019042</v>
+        <v>-23.94410913940828</v>
       </c>
       <c r="F25">
-        <v>-1.585298204763895</v>
+        <v>-1.13829872870224</v>
       </c>
       <c r="G25">
-        <v>-6.699946113410609</v>
+        <v>-3.662666245133022</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.257751064864409</v>
       </c>
       <c r="E26">
-        <v>-26.08916123583558</v>
+        <v>-23.42637323458533</v>
       </c>
       <c r="F26">
-        <v>-1.760014143892756</v>
+        <v>-1.379089393715403</v>
       </c>
       <c r="G26">
-        <v>-6.483297392229623</v>
+        <v>-4.52491107301836</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.962332215702004</v>
       </c>
       <c r="E27">
-        <v>-28.20519939929574</v>
+        <v>-24.13204533920061</v>
       </c>
       <c r="F27">
-        <v>-1.313463642963418</v>
+        <v>-0.8251452008501233</v>
       </c>
       <c r="G27">
-        <v>-7.652396686150007</v>
+        <v>-4.544694893161044</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.634730085769145</v>
       </c>
       <c r="E28">
-        <v>-26.33587702824747</v>
+        <v>-23.36351348688486</v>
       </c>
       <c r="F28">
-        <v>-1.103822905765127</v>
+        <v>-1.209692401679918</v>
       </c>
       <c r="G28">
-        <v>-6.344459733403668</v>
+        <v>-4.16474358161889</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.2931118965601</v>
       </c>
       <c r="E29">
-        <v>-26.22356181590923</v>
+        <v>-22.95086534988392</v>
       </c>
       <c r="F29">
-        <v>-1.739957712336174</v>
+        <v>-0.9273110661069975</v>
       </c>
       <c r="G29">
-        <v>-6.905921635772983</v>
+        <v>-4.187010310916029</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.952602959533158</v>
       </c>
       <c r="E30">
-        <v>-25.51156796157925</v>
+        <v>-22.90320316095319</v>
       </c>
       <c r="F30">
-        <v>-1.286157339897535</v>
+        <v>-0.8686253774556666</v>
       </c>
       <c r="G30">
-        <v>-6.902525016049691</v>
+        <v>-5.130065555414976</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.626368956069854</v>
       </c>
       <c r="E31">
-        <v>-25.96754453788559</v>
+        <v>-23.30696643195108</v>
       </c>
       <c r="F31">
-        <v>-1.201450974389466</v>
+        <v>-0.9393555281437024</v>
       </c>
       <c r="G31">
-        <v>-7.904037873681089</v>
+        <v>-4.808499025003409</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.326992613398241</v>
       </c>
       <c r="E32">
-        <v>-25.18645522714657</v>
+        <v>-22.01268327581882</v>
       </c>
       <c r="F32">
-        <v>-1.252132148827545</v>
+        <v>-0.6820472171187171</v>
       </c>
       <c r="G32">
-        <v>-7.164521590027612</v>
+        <v>-5.173148995063051</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.066731631799716</v>
       </c>
       <c r="E33">
-        <v>-24.61618449536065</v>
+        <v>-21.54422169667334</v>
       </c>
       <c r="F33">
-        <v>-1.387118758950739</v>
+        <v>-1.172439062841219</v>
       </c>
       <c r="G33">
-        <v>-7.359453132470978</v>
+        <v>-4.65441299342357</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.8520118099166336</v>
       </c>
       <c r="E34">
-        <v>-25.31787154284917</v>
+        <v>-21.4326808533904</v>
       </c>
       <c r="F34">
-        <v>-1.099141801571907</v>
+        <v>-1.112374142464227</v>
       </c>
       <c r="G34">
-        <v>-7.080221858415611</v>
+        <v>-4.272515081104324</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.6847382851213756</v>
       </c>
       <c r="E35">
-        <v>-25.02639178487146</v>
+        <v>-21.10086597742638</v>
       </c>
       <c r="F35">
-        <v>-1.023271631149501</v>
+        <v>-1.39477701558962</v>
       </c>
       <c r="G35">
-        <v>-6.930760658954135</v>
+        <v>-4.244809125486164</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.5655129237606457</v>
       </c>
       <c r="E36">
-        <v>-24.44880756756314</v>
+        <v>-21.15470047642956</v>
       </c>
       <c r="F36">
-        <v>-1.264773035394266</v>
+        <v>-1.355074194340843</v>
       </c>
       <c r="G36">
-        <v>-6.772976748006931</v>
+        <v>-4.256737021064159</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.4910855800477102</v>
       </c>
       <c r="E37">
-        <v>-24.95966924884244</v>
+        <v>-19.76208603569474</v>
       </c>
       <c r="F37">
-        <v>-1.699333746535484</v>
+        <v>-1.299398792831285</v>
       </c>
       <c r="G37">
-        <v>-7.468363459621922</v>
+        <v>-4.265625835837102</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.4540686685144974</v>
       </c>
       <c r="E38">
-        <v>-22.99840979849045</v>
+        <v>-19.38518114403634</v>
       </c>
       <c r="F38">
-        <v>-1.098552832348517</v>
+        <v>-1.288094891252683</v>
       </c>
       <c r="G38">
-        <v>-7.265357496608273</v>
+        <v>-3.967941580945836</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.4455444040552302</v>
       </c>
       <c r="E39">
-        <v>-23.79361889118538</v>
+        <v>-19.10730492197767</v>
       </c>
       <c r="F39">
-        <v>-0.8899608082821706</v>
+        <v>-1.071614324409477</v>
       </c>
       <c r="G39">
-        <v>-6.940298340652775</v>
+        <v>-3.460501160686348</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.4585434599066843</v>
       </c>
       <c r="E40">
-        <v>-21.94921671260132</v>
+        <v>-19.30110096713592</v>
       </c>
       <c r="F40">
-        <v>-1.706518177019964</v>
+        <v>-0.9464306141310129</v>
       </c>
       <c r="G40">
-        <v>-7.015884716405415</v>
+        <v>-3.750584403019447</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.4843589193653284</v>
       </c>
       <c r="E41">
-        <v>-21.69050952101712</v>
+        <v>-18.80422321359231</v>
       </c>
       <c r="F41">
-        <v>-1.107081703127741</v>
+        <v>-0.9347373798730951</v>
       </c>
       <c r="G41">
-        <v>-5.202960457644188</v>
+        <v>-3.219178943601175</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.5143126468548737</v>
       </c>
       <c r="E42">
-        <v>-23.03618632866243</v>
+        <v>-18.22538913745787</v>
       </c>
       <c r="F42">
-        <v>-1.24254048267053</v>
+        <v>-1.446814227466082</v>
       </c>
       <c r="G42">
-        <v>-6.30248201596571</v>
+        <v>-3.81884454149368</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.5403414452925199</v>
       </c>
       <c r="E43">
-        <v>-20.40276548135193</v>
+        <v>-17.49767242137327</v>
       </c>
       <c r="F43">
-        <v>-1.076638372707456</v>
+        <v>-1.023018979091647</v>
       </c>
       <c r="G43">
-        <v>-6.72751302611612</v>
+        <v>-3.359287851914211</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.5563699841243146</v>
       </c>
       <c r="E44">
-        <v>-19.89995542685827</v>
+        <v>-17.5881377466245</v>
       </c>
       <c r="F44">
-        <v>-1.630161754932114</v>
+        <v>-1.284216475072776</v>
       </c>
       <c r="G44">
-        <v>-7.438442749037989</v>
+        <v>-3.460818973058119</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.5562799056830808</v>
       </c>
       <c r="E45">
-        <v>-20.54596035794847</v>
+        <v>-16.71975757091363</v>
       </c>
       <c r="F45">
-        <v>-1.451320546137312</v>
+        <v>-1.307846483605034</v>
       </c>
       <c r="G45">
-        <v>-7.27322997390066</v>
+        <v>-3.646424708717358</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.5348910780211762</v>
       </c>
       <c r="E46">
-        <v>-20.86290825374532</v>
+        <v>-14.61293938053309</v>
       </c>
       <c r="F46">
-        <v>-1.555288110495275</v>
+        <v>-1.485439342723818</v>
       </c>
       <c r="G46">
-        <v>-6.441551412979414</v>
+        <v>-3.707401647005194</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.4881121188500033</v>
       </c>
       <c r="E47">
-        <v>-19.46158555749375</v>
+        <v>-15.69803420835503</v>
       </c>
       <c r="F47">
-        <v>-1.245472074909037</v>
+        <v>-1.385276469846913</v>
       </c>
       <c r="G47">
-        <v>-6.387854364332435</v>
+        <v>-3.72617906130394</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.413830393955006</v>
       </c>
       <c r="E48">
-        <v>-19.83978559271835</v>
+        <v>-16.1829024488303</v>
       </c>
       <c r="F48">
-        <v>-1.427138844914788</v>
+        <v>-1.446693285825273</v>
       </c>
       <c r="G48">
-        <v>-5.971126202394517</v>
+        <v>-3.792171476083772</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.3123905548293549</v>
       </c>
       <c r="E49">
-        <v>-19.05954763509278</v>
+        <v>-15.29084741100733</v>
       </c>
       <c r="F49">
-        <v>-1.449762387052646</v>
+        <v>-1.222039217818645</v>
       </c>
       <c r="G49">
-        <v>-7.935825731949171</v>
+        <v>-3.559602341404432</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.1846067312287128</v>
       </c>
       <c r="E50">
-        <v>-17.43078686027997</v>
+        <v>-15.03196360893683</v>
       </c>
       <c r="F50">
-        <v>-1.954139559636612</v>
+        <v>-1.193458885687256</v>
       </c>
       <c r="G50">
-        <v>-5.825501925213056</v>
+        <v>-3.803847770200781</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.03323428515203291</v>
       </c>
       <c r="E51">
-        <v>-18.42816514657334</v>
+        <v>-13.21522134959162</v>
       </c>
       <c r="F51">
-        <v>-1.375332747543707</v>
+        <v>-1.423647276311989</v>
       </c>
       <c r="G51">
-        <v>-6.97693283759035</v>
+        <v>-4.270687659966647</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.1374872854948235</v>
       </c>
       <c r="E52">
-        <v>-15.90196497834244</v>
+        <v>-13.20407224658474</v>
       </c>
       <c r="F52">
-        <v>-1.757602766383206</v>
+        <v>-1.519208568266342</v>
       </c>
       <c r="G52">
-        <v>-7.407727507524631</v>
+        <v>-4.118286696066298</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.3214202346653517</v>
       </c>
       <c r="E53">
-        <v>-16.26660223391407</v>
+        <v>-13.64870046702785</v>
       </c>
       <c r="F53">
-        <v>-1.528566634815768</v>
+        <v>-1.603977889697024</v>
       </c>
       <c r="G53">
-        <v>-7.268346919230235</v>
+        <v>-4.498900116716306</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.5138832442860016</v>
       </c>
       <c r="E54">
-        <v>-16.73807977674866</v>
+        <v>-13.29661614140549</v>
       </c>
       <c r="F54">
-        <v>-1.914874944743915</v>
+        <v>-1.273576924151219</v>
       </c>
       <c r="G54">
-        <v>-8.36127056029199</v>
+        <v>-4.575565730314748</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.7085604786489589</v>
       </c>
       <c r="E55">
-        <v>-16.08333036234964</v>
+        <v>-12.23717059036299</v>
       </c>
       <c r="F55">
-        <v>-1.204684092362592</v>
+        <v>-1.625657921363093</v>
       </c>
       <c r="G55">
-        <v>-7.815348358684014</v>
+        <v>-4.783656691276717</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.8989064976584464</v>
       </c>
       <c r="E56">
-        <v>-16.23945856071209</v>
+        <v>-12.27266476963511</v>
       </c>
       <c r="F56">
-        <v>-1.370203496585573</v>
+        <v>-1.364904430309864</v>
       </c>
       <c r="G56">
-        <v>-7.321143499490533</v>
+        <v>-4.655346567265645</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.078965000323877</v>
       </c>
       <c r="E57">
-        <v>-16.52064962574438</v>
+        <v>-11.74328162966444</v>
       </c>
       <c r="F57">
-        <v>-2.021901669920417</v>
+        <v>-1.545833953327124</v>
       </c>
       <c r="G57">
-        <v>-8.522573581147439</v>
+        <v>-4.436009683106771</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.245674726979868</v>
       </c>
       <c r="E58">
-        <v>-15.68899537423572</v>
+        <v>-12.09346852467759</v>
       </c>
       <c r="F58">
-        <v>-1.01995153459908</v>
+        <v>-1.616086964391147</v>
       </c>
       <c r="G58">
-        <v>-7.340453911621101</v>
+        <v>-5.247523711148317</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.396291609462962</v>
       </c>
       <c r="E59">
-        <v>-15.53923873880206</v>
+        <v>-12.35845218123642</v>
       </c>
       <c r="F59">
-        <v>-0.9150139520124388</v>
+        <v>-1.676882504817409</v>
       </c>
       <c r="G59">
-        <v>-8.032659188972852</v>
+        <v>-5.061053923103329</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.528718576003065</v>
       </c>
       <c r="E60">
-        <v>-15.55230338631419</v>
+        <v>-11.67590246490431</v>
       </c>
       <c r="F60">
-        <v>-1.18031020990262</v>
+        <v>-1.456736412216815</v>
       </c>
       <c r="G60">
-        <v>-8.568335252136785</v>
+        <v>-4.726278315990069</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.643699172658442</v>
       </c>
       <c r="E61">
-        <v>-14.8290291032311</v>
+        <v>-11.27073989543805</v>
       </c>
       <c r="F61">
-        <v>-1.741835621238321</v>
+        <v>-2.025249102595129</v>
       </c>
       <c r="G61">
-        <v>-9.382583790793769</v>
+        <v>-4.914178259708023</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.744232783138201</v>
       </c>
       <c r="E62">
-        <v>-14.73487307166362</v>
+        <v>-11.1592443368952</v>
       </c>
       <c r="F62">
-        <v>-1.558203135385726</v>
+        <v>-1.654548891270531</v>
       </c>
       <c r="G62">
-        <v>-7.937388309443707</v>
+        <v>-5.830325390063774</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.834077385527428</v>
       </c>
       <c r="E63">
-        <v>-15.40318979418962</v>
+        <v>-10.54053704712322</v>
       </c>
       <c r="F63">
-        <v>-1.649157047845709</v>
+        <v>-1.576493487639539</v>
       </c>
       <c r="G63">
-        <v>-8.497655104873346</v>
+        <v>-4.513476448725718</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.915097494078939</v>
       </c>
       <c r="E64">
-        <v>-15.15867936861946</v>
+        <v>-10.82021560183695</v>
       </c>
       <c r="F64">
-        <v>-1.72270861790768</v>
+        <v>-1.626876449812611</v>
       </c>
       <c r="G64">
-        <v>-8.858607195565622</v>
+        <v>-5.136305933756502</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.991801318885706</v>
       </c>
       <c r="E65">
-        <v>-14.79290093759791</v>
+        <v>-10.97474524887469</v>
       </c>
       <c r="F65">
-        <v>-1.726954000847027</v>
+        <v>-1.917599445131722</v>
       </c>
       <c r="G65">
-        <v>-8.499323619825137</v>
+        <v>-5.077967500263465</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.068170893922347</v>
       </c>
       <c r="E66">
-        <v>-13.45027632143376</v>
+        <v>-11.16160367185319</v>
       </c>
       <c r="F66">
-        <v>-1.547929722856207</v>
+        <v>-1.943418000342177</v>
       </c>
       <c r="G66">
-        <v>-8.202420653681139</v>
+        <v>-5.372956971085763</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.147209133672707</v>
       </c>
       <c r="E67">
-        <v>-13.63571280357385</v>
+        <v>-10.51464776122137</v>
       </c>
       <c r="F67">
-        <v>-1.630581737205333</v>
+        <v>-1.757682289653875</v>
       </c>
       <c r="G67">
-        <v>-8.116713940214948</v>
+        <v>-5.192946057387893</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.229003591741826</v>
       </c>
       <c r="E68">
-        <v>-13.83147873492544</v>
+        <v>-10.751763188737</v>
       </c>
       <c r="F68">
-        <v>-2.30241669373483</v>
+        <v>-1.803658337244053</v>
       </c>
       <c r="G68">
-        <v>-8.417271748634301</v>
+        <v>-5.034152430051211</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.31572661423384</v>
       </c>
       <c r="E69">
-        <v>-13.85602759252102</v>
+        <v>-10.34580813631939</v>
       </c>
       <c r="F69">
-        <v>-1.738715989599378</v>
+        <v>-1.946107709299068</v>
       </c>
       <c r="G69">
-        <v>-9.139646027485432</v>
+        <v>-5.125424170568918</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.409260817146643</v>
       </c>
       <c r="E70">
-        <v>-14.08751412684512</v>
+        <v>-10.1710588528374</v>
       </c>
       <c r="F70">
-        <v>-1.841397099380793</v>
+        <v>-2.080707471845153</v>
       </c>
       <c r="G70">
-        <v>-8.785818230793666</v>
+        <v>-5.256283414645229</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.508879538253395</v>
       </c>
       <c r="E71">
-        <v>-14.58181065020436</v>
+        <v>-10.53886151174039</v>
       </c>
       <c r="F71">
-        <v>-2.114583556782639</v>
+        <v>-1.850573753469006</v>
       </c>
       <c r="G71">
-        <v>-8.289488001363972</v>
+        <v>-5.215994075432299</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.612578471837197</v>
       </c>
       <c r="E72">
-        <v>-12.99306800019734</v>
+        <v>-11.28806130851739</v>
       </c>
       <c r="F72">
-        <v>-2.408586887016837</v>
+        <v>-1.835573676539113</v>
       </c>
       <c r="G72">
-        <v>-7.784576837896489</v>
+        <v>-5.330711099459124</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.719386923386724</v>
       </c>
       <c r="E73">
-        <v>-15.61369590843617</v>
+        <v>-11.15998700663245</v>
       </c>
       <c r="F73">
-        <v>-1.859534203665088</v>
+        <v>-1.898008556055514</v>
       </c>
       <c r="G73">
-        <v>-7.711082726924668</v>
+        <v>-4.496880683937351</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.827767456373957</v>
       </c>
       <c r="E74">
-        <v>-15.1518549582899</v>
+        <v>-10.98056433797455</v>
       </c>
       <c r="F74">
-        <v>-2.729913087664974</v>
+        <v>-2.116898843673464</v>
       </c>
       <c r="G74">
-        <v>-7.96844453714761</v>
+        <v>-4.537789095166125</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.932027798033109</v>
       </c>
       <c r="E75">
-        <v>-15.96368355059298</v>
+        <v>-12.25864914258137</v>
       </c>
       <c r="F75">
-        <v>-2.055753732203221</v>
+        <v>-2.32886977837583</v>
       </c>
       <c r="G75">
-        <v>-7.733475256952298</v>
+        <v>-4.649241921291229</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.026783234268094</v>
       </c>
       <c r="E76">
-        <v>-14.64502361887743</v>
+        <v>-12.5030825840934</v>
       </c>
       <c r="F76">
-        <v>-2.483601353912152</v>
+        <v>-2.290561927833366</v>
       </c>
       <c r="G76">
-        <v>-7.456412390225153</v>
+        <v>-4.485283842913284</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.107747465660917</v>
       </c>
       <c r="E77">
-        <v>-15.99554589371095</v>
+        <v>-12.74672807112809</v>
       </c>
       <c r="F77">
-        <v>-2.816874269243463</v>
+        <v>-2.380705696973411</v>
       </c>
       <c r="G77">
-        <v>-7.811772969501601</v>
+        <v>-4.530985924082922</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.170715573406875</v>
       </c>
       <c r="E78">
-        <v>-15.82880295227452</v>
+        <v>-12.69002704807805</v>
       </c>
       <c r="F78">
-        <v>-2.478955041149849</v>
+        <v>-2.266733111124436</v>
       </c>
       <c r="G78">
-        <v>-7.111182080298875</v>
+        <v>-4.171675863978124</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.209113492463989</v>
       </c>
       <c r="E79">
-        <v>-16.02995776769524</v>
+        <v>-13.49604560822928</v>
       </c>
       <c r="F79">
-        <v>-2.662875798858618</v>
+        <v>-2.827372169339141</v>
       </c>
       <c r="G79">
-        <v>-6.448976966623999</v>
+        <v>-4.525513592306507</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.219680338624366</v>
       </c>
       <c r="E80">
-        <v>-16.31313683281689</v>
+        <v>-13.89968661042897</v>
       </c>
       <c r="F80">
-        <v>-3.164795205358478</v>
+        <v>-2.92234035023309</v>
       </c>
       <c r="G80">
-        <v>-6.831811763330858</v>
+        <v>-4.235208543422278</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.201442613064951</v>
       </c>
       <c r="E81">
-        <v>-17.31061474553843</v>
+        <v>-14.37504505548814</v>
       </c>
       <c r="F81">
-        <v>-2.81523410178592</v>
+        <v>-2.593081703335746</v>
       </c>
       <c r="G81">
-        <v>-7.918809527877317</v>
+        <v>-3.716485783964954</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.153759489619847</v>
       </c>
       <c r="E82">
-        <v>-18.98391306221667</v>
+        <v>-15.56198526374259</v>
       </c>
       <c r="F82">
-        <v>-2.962165769857482</v>
+        <v>-2.905025814779775</v>
       </c>
       <c r="G82">
-        <v>-6.35590097878739</v>
+        <v>-4.598524363629594</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.076200466764238</v>
       </c>
       <c r="E83">
-        <v>-19.37154590879924</v>
+        <v>-16.49436636260386</v>
       </c>
       <c r="F83">
-        <v>-3.25072175605087</v>
+        <v>-2.447548319440109</v>
       </c>
       <c r="G83">
-        <v>-6.163263644402739</v>
+        <v>-3.953484428575839</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.970977947756444</v>
       </c>
       <c r="E84">
-        <v>-19.30318859365346</v>
+        <v>-17.00389667252491</v>
       </c>
       <c r="F84">
-        <v>-2.870343728359365</v>
+        <v>-2.927356114857041</v>
       </c>
       <c r="G84">
-        <v>-5.630219464942527</v>
+        <v>-4.029938167259767</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.84447854906462</v>
       </c>
       <c r="E85">
-        <v>-21.44899694524004</v>
+        <v>-17.42368168456194</v>
       </c>
       <c r="F85">
-        <v>-3.266066433820328</v>
+        <v>-2.825875309442282</v>
       </c>
       <c r="G85">
-        <v>-6.370103219150863</v>
+        <v>-4.217761968430318</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.701421835822258</v>
       </c>
       <c r="E86">
-        <v>-21.57810826767273</v>
+        <v>-18.734969260593</v>
       </c>
       <c r="F86">
-        <v>-3.220478890542063</v>
+        <v>-2.889477358629228</v>
       </c>
       <c r="G86">
-        <v>-7.09589729154406</v>
+        <v>-3.732002310907518</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.546520538752364</v>
       </c>
       <c r="E87">
-        <v>-22.22263691623644</v>
+        <v>-19.2522025048011</v>
       </c>
       <c r="F87">
-        <v>-3.462947827913298</v>
+        <v>-2.926136758040121</v>
       </c>
       <c r="G87">
-        <v>-6.216464111218826</v>
+        <v>-4.120200191387997</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.385996434083284</v>
       </c>
       <c r="E88">
-        <v>-23.21031068273137</v>
+        <v>-20.71897976435953</v>
       </c>
       <c r="F88">
-        <v>-3.689441699921545</v>
+        <v>-2.789697191492417</v>
       </c>
       <c r="G88">
-        <v>-5.92528176776669</v>
+        <v>-4.033434103349238</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.228692234146607</v>
       </c>
       <c r="E89">
-        <v>-25.41255287740154</v>
+        <v>-21.60740296602835</v>
       </c>
       <c r="F89">
-        <v>-3.327651408381458</v>
+        <v>-3.162846885227093</v>
       </c>
       <c r="G89">
-        <v>-7.002334653513178</v>
+        <v>-3.589244966163066</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.080264035382435</v>
       </c>
       <c r="E90">
-        <v>-25.84854529791203</v>
+        <v>-23.72622161252922</v>
       </c>
       <c r="F90">
-        <v>-3.455523999249409</v>
+        <v>-3.011636699520071</v>
       </c>
       <c r="G90">
-        <v>-6.798898319579425</v>
+        <v>-4.286687526557944</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.946528264875682</v>
       </c>
       <c r="E91">
-        <v>-29.51914518956931</v>
+        <v>-24.75947899838536</v>
       </c>
       <c r="F91">
-        <v>-3.768781901394278</v>
+        <v>-3.01936205391858</v>
       </c>
       <c r="G91">
-        <v>-6.411094394018119</v>
+        <v>-4.078139710311556</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.834628497179552</v>
       </c>
       <c r="E92">
-        <v>-30.66748921385638</v>
+        <v>-27.52035827511575</v>
       </c>
       <c r="F92">
-        <v>-3.496332690980924</v>
+        <v>-3.281582583642166</v>
       </c>
       <c r="G92">
-        <v>-6.352606985975815</v>
+        <v>-4.642839326218279</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.750782994571358</v>
       </c>
       <c r="E93">
-        <v>-32.34763005476022</v>
+        <v>-27.64345578406625</v>
       </c>
       <c r="F93">
-        <v>-3.459848077092023</v>
+        <v>-3.131408685556047</v>
       </c>
       <c r="G93">
-        <v>-7.182802422495469</v>
+        <v>-4.629633560062126</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.695953146799063</v>
       </c>
       <c r="E94">
-        <v>-33.35598989052218</v>
+        <v>-30.42535623714026</v>
       </c>
       <c r="F94">
-        <v>-3.943102709272003</v>
+        <v>-3.220196417257709</v>
       </c>
       <c r="G94">
-        <v>-7.230189571344596</v>
+        <v>-4.782037834508014</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.670450044359575</v>
       </c>
       <c r="E95">
-        <v>-35.71395045665711</v>
+        <v>-32.0332996169398</v>
       </c>
       <c r="F95">
-        <v>-3.122136769216512</v>
+        <v>-3.32531458393816</v>
       </c>
       <c r="G95">
-        <v>-7.988648796573782</v>
+        <v>-4.426051562124644</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.67500621495229</v>
       </c>
       <c r="E96">
-        <v>-38.08785351553604</v>
+        <v>-34.04776410840791</v>
       </c>
       <c r="F96">
-        <v>-3.948130071039594</v>
+        <v>-3.118723067149575</v>
       </c>
       <c r="G96">
-        <v>-6.670571642840655</v>
+        <v>-4.837148486100261</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.706127124642072</v>
       </c>
       <c r="E97">
-        <v>-38.15097817896596</v>
+        <v>-36.34664393840177</v>
       </c>
       <c r="F97">
-        <v>-4.270276355416502</v>
+        <v>-3.011801544633228</v>
       </c>
       <c r="G97">
-        <v>-8.347419237755679</v>
+        <v>-6.038949348857567</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.759249405936505</v>
       </c>
       <c r="E98">
-        <v>-41.16221640544742</v>
+        <v>-37.34800048911087</v>
       </c>
       <c r="F98">
-        <v>-3.598255016221375</v>
+        <v>-3.435914057722936</v>
       </c>
       <c r="G98">
-        <v>-8.186371128906753</v>
+        <v>-5.591568845771536</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.828883385977349</v>
       </c>
       <c r="E99">
-        <v>-43.72388584634339</v>
+        <v>-40.56235436025837</v>
       </c>
       <c r="F99">
-        <v>-4.377114212825165</v>
+        <v>-3.242250870989843</v>
       </c>
       <c r="G99">
-        <v>-8.349928631274446</v>
+        <v>-6.294066609204882</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.915738673201168</v>
       </c>
       <c r="E100">
-        <v>-44.09208021824804</v>
+        <v>-43.46245251340657</v>
       </c>
       <c r="F100">
-        <v>-3.618591435960103</v>
+        <v>-3.5211514067362</v>
       </c>
       <c r="G100">
-        <v>-8.610154063388858</v>
+        <v>-6.325175805637413</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.011762405690766</v>
       </c>
       <c r="E101">
-        <v>-48.58731296246509</v>
+        <v>-44.62734811019168</v>
       </c>
       <c r="F101">
-        <v>-3.792995908945511</v>
+        <v>-3.688127909220705</v>
       </c>
       <c r="G101">
-        <v>-7.657984887020297</v>
+        <v>-7.049751597272159</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.119370659216971</v>
       </c>
       <c r="E102">
-        <v>-47.89657802936412</v>
+        <v>-47.02181270530244</v>
       </c>
       <c r="F102">
-        <v>-4.283267641394606</v>
+        <v>-3.443766980701476</v>
       </c>
       <c r="G102">
-        <v>-8.715826677002395</v>
+        <v>-7.043832341847942</v>
       </c>
     </row>
   </sheetData>
